--- a/excel/pardadex_ccc.xlsx
+++ b/excel/pardadex_ccc.xlsx
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24984</v>
+        <v>69554</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -643,17 +643,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C001452822</t>
+          <t>C004164790</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C001452822 - FERNANDEZ CABRERA LUISA</t>
+          <t>C004164790 - CERQUERA MARLO LUZ ELINA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>S17842798</t>
+          <t>S17850556</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -682,11 +682,11 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69554</v>
+        <v>24984</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -883,17 +883,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C004164790</t>
+          <t>C001452822</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C004164790 - CERQUERA MARLO LUZ ELINA</t>
+          <t>C001452822 - FERNANDEZ CABRERA LUISA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>S17850556</t>
+          <t>S17842798</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -922,11 +922,11 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100658</v>
+        <v>28854</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C004172041</t>
+          <t>C001474582</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C004172041 - RAMIREZ PALACIOS ANTONIA ROSALIA</t>
+          <t>C001474582 - MCCUBY MIRANDA ROSA ELENA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>S17805314</t>
+          <t>S17816501</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,11 +1042,11 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1089,16 +1089,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109154</v>
+        <v>31182</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C001077720</t>
+          <t>C001075708</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C001077720 - BRAVO CHOZO TOMAS</t>
+          <t>C001075708 - CUEVA DE ESTRADA GENARA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>S17815550</t>
+          <t>S17804274</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1162,11 +1162,11 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>77666</v>
+        <v>42512</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C001733538</t>
+          <t>C001719557</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C001733538 - FARFAN RELAIZA YTALA</t>
+          <t>C001719557 - MIMBELA RODAS MARHIA BELEN</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>S17817338</t>
+          <t>S17808803</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1329,16 +1329,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>42512</v>
+        <v>60693</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C001719557</t>
+          <t>C004172093</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C001719557 - MIMBELA RODAS MARHIA BELEN</t>
+          <t>C004172093 - ALDANA GARCIA TEODOCIA YSABEL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>S17808803</t>
+          <t>S17831411</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,11 +1402,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1449,16 +1449,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60693</v>
+        <v>100658</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C004172093</t>
+          <t>C004172041</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C004172093 - ALDANA GARCIA TEODOCIA YSABEL</t>
+          <t>C004172041 - RAMIREZ PALACIOS ANTONIA ROSALIA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>S17831411</t>
+          <t>S17805314</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,11 +1522,11 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1569,16 +1569,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>28854</v>
+        <v>109154</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C001474582</t>
+          <t>C001077720</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C001474582 - MCCUBY MIRANDA ROSA ELENA</t>
+          <t>C001077720 - BRAVO CHOZO TOMAS</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S17816501</t>
+          <t>S17815550</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1642,11 +1642,11 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>31182</v>
+        <v>77666</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C001075708</t>
+          <t>C001733538</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C001075708 - CUEVA DE ESTRADA GENARA</t>
+          <t>C001733538 - FARFAN RELAIZA YTALA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>S17804274</t>
+          <t>S17817338</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1809,16 +1809,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15676</v>
+        <v>88093</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C001098581</t>
+          <t>C004241151</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C001098581 - ROSALES RIOS PRUDENCIO JAIME</t>
+          <t>C004241151 - TERAN CAYAO MAGALY</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>S17773502</t>
+          <t>S17777143</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1882,11 +1882,11 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1929,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9635</v>
+        <v>105461</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C001076973</t>
+          <t>C001075936</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C001076973 - FIESTAS BAZAN CECILIA PILAR</t>
+          <t>C001075936 - FIESTAS BAZAN NELLY</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>S17787002</t>
+          <t>S17787859</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -2289,16 +2289,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>88093</v>
+        <v>15676</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C004241151</t>
+          <t>C001098581</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C004241151 - TERAN CAYAO MAGALY</t>
+          <t>C001098581 - ROSALES RIOS PRUDENCIO JAIME</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>S17777143</t>
+          <t>S17773502</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2362,11 +2362,11 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105461</v>
+        <v>9635</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C001075936</t>
+          <t>C001076973</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C001075936 - FIESTAS BAZAN NELLY</t>
+          <t>C001076973 - FIESTAS BAZAN CECILIA PILAR</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>S17787859</t>
+          <t>S17787002</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -2529,16 +2529,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106564</v>
+        <v>44725</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C001680523</t>
+          <t>C001732991</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C001680523 - ALCANTARA HUERTAS SARA NOEMI</t>
+          <t>C001732991 - GASTULO ANTON ANA MARIA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>S17743694</t>
+          <t>S17742312</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2602,11 +2602,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2649,16 +2649,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103401</v>
+        <v>46751</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C001731912</t>
+          <t>C001736067</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C001731912 - GONZALES MONTEZA ERIKA JUDITH</t>
+          <t>C001736067 - ANCAJIMA SARRIN JORGE ERICKSON</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>S17740676</t>
+          <t>S17752075</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2722,11 +2722,11 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2743,11 +2743,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
@@ -2769,16 +2765,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>70469</v>
+        <v>56419</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2803,12 +2799,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C004061734</t>
+          <t>C001734798</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C004061734 - MEJIA SAAVEDRA NANCY ELIZABETH</t>
+          <t>C001734798 - MANAYALLE CABRERA SILVIA ELIANA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2832,7 +2828,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>S17749146</t>
+          <t>S17763504</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,11 +2838,11 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2865,7 +2861,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -2877,7 +2873,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2889,16 +2885,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46751</v>
+        <v>62329</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2923,12 +2919,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C001736067</t>
+          <t>C001737414</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C001736067 - ANCAJIMA SARRIN JORGE ERICKSON</t>
+          <t>C001737414 - BRIONES DAMIAN LILA DEL CARMEN</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2952,7 +2948,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>S17752075</t>
+          <t>S17758898</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2962,11 +2958,11 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2983,7 +2979,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
@@ -3005,7 +3005,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>44725</v>
+        <v>103401</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3039,12 +3039,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C001732991</t>
+          <t>C001731912</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C001732991 - GASTULO ANTON ANA MARIA</t>
+          <t>C001731912 - GONZALES MONTEZA ERIKA JUDITH</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>S17742312</t>
+          <t>S17740676</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3125,16 +3125,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>56419</v>
+        <v>106564</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C001734798</t>
+          <t>C001680523</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C001734798 - MANAYALLE CABRERA SILVIA ELIANA</t>
+          <t>C001680523 - ALCANTARA HUERTAS SARA NOEMI</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>S17763504</t>
+          <t>S17743694</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3198,11 +3198,11 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -3245,16 +3245,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>62329</v>
+        <v>70469</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C001737414</t>
+          <t>C004061734</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C001737414 - BRIONES DAMIAN LILA DEL CARMEN</t>
+          <t>C004061734 - MEJIA SAAVEDRA NANCY ELIZABETH</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>S17758898</t>
+          <t>S17749146</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3485,7 +3485,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7920</v>
+        <v>67980</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C001081307</t>
+          <t>C001696221</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C001081307 - SANTISTEBAN SANCHEZ VIOLETA</t>
+          <t>C001696221 - VENTURA SUCLUPE MARIA FILOMENA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S17629685</t>
+          <t>S17620618</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3601,16 +3601,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>28008</v>
+        <v>92739</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3625,22 +3625,22 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C001452413</t>
+          <t>C004177292</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C001452413 - CHANDUVI PUICON SONIA VIOLETA</t>
+          <t>C004177292 - SAAVEDRA CASTILLO GLORIA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3660,11 +3660,11 @@
         <v>46235</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>S17631359</t>
+          <t>S17679352</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3674,11 +3674,11 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3698,23 +3698,35 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>64558</v>
+        <v>105228</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3739,12 +3751,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C001765640</t>
+          <t>C001079722</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C001765640 - CATON CORDOVA NURY ADITA</t>
+          <t>C001079722 - VASQUEZ CAPU AY MANUEL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3768,7 +3780,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>S17628016</t>
+          <t>S17614493</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3778,11 +3790,11 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3791,7 +3803,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3799,7 +3811,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
@@ -3821,7 +3837,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>56797</v>
+        <v>7920</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3845,22 +3861,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C001745658</t>
+          <t>C001081307</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C001745658 - BRAVO PISCOYA MARIA GRIMALDINA</t>
+          <t>C001081307 - SANTISTEBAN SANCHEZ VIOLETA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3884,7 +3900,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17630851</t>
+          <t>S17629685</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3915,21 +3931,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67980</v>
+        <v>28008</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3953,22 +3977,22 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C001696221</t>
+          <t>C001452413</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C001696221 - VENTURA SUCLUPE MARIA FILOMENA</t>
+          <t>C001452413 - CHANDUVI PUICON SONIA VIOLETA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3992,7 +4016,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>S17620618</t>
+          <t>S17631359</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4026,26 +4050,14 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>92739</v>
+        <v>64558</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4079,12 +4091,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C004177292</t>
+          <t>C001765640</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C004177292 - SAAVEDRA CASTILLO GLORIA</t>
+          <t>C001765640 - CATON CORDOVA NURY ADITA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4104,11 +4116,11 @@
         <v>46235</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17679352</t>
+          <t>S17628016</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4131,7 +4143,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4144,7 +4156,7 @@
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4161,7 +4173,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105228</v>
+        <v>56797</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4185,22 +4197,22 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C001079722</t>
+          <t>C001745658</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C001079722 - VASQUEZ CAPU AY MANUEL</t>
+          <t>C001745658 - BRAVO PISCOYA MARIA GRIMALDINA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4224,7 +4236,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17614493</t>
+          <t>S17630851</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4247,7 +4259,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4262,26 +4274,14 @@
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110156</v>
+        <v>65755</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4315,12 +4315,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C001553531</t>
+          <t>C004166296</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C001553531 - RIVAS ARRIAGA JOSE RICARDO</t>
+          <t>C004166296 - BRIONES SUSANIVAR RUDY GIAMPIER</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4340,11 +4340,11 @@
         <v>46235</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>S17623184</t>
+          <t>S17712210</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4397,7 +4397,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111438</v>
+        <v>61124</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4431,17 +4431,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C001274655</t>
+          <t>C001740301</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C001274655 - MARTINEZ SOPLAPUCO PEDRO</t>
+          <t>C001740301 - GUERRERO PAREDES MERCEDES ISABEL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4456,11 +4456,11 @@
         <v>46235</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>S17593174</t>
+          <t>S17732719</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4470,11 +4470,11 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4491,11 +4491,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr">
@@ -4517,7 +4513,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>82417</v>
+        <v>36090</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4551,17 +4547,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C004180367</t>
+          <t>C001628093</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C004180367 - HUAYTAN CAICEDO WALTER ORLANDO</t>
+          <t>C001628093 - CRUZ MORANTE LUIS</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4576,11 +4572,11 @@
         <v>46235</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>S17673606</t>
+          <t>S17730841</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4590,11 +4586,11 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -4633,7 +4629,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>65755</v>
+        <v>28142</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4667,12 +4663,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C004166296</t>
+          <t>C001521360</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C004166296 - BRIONES SUSANIVAR RUDY GIAMPIER</t>
+          <t>C001521360 - CARLOS DE LA CRUZ SERGIO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4692,11 +4688,11 @@
         <v>46235</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>S17712210</t>
+          <t>S17617098</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4749,16 +4745,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>61124</v>
+        <v>20014</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4783,17 +4779,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C001740301</t>
+          <t>C001301555</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C001740301 - GUERRERO PAREDES MERCEDES ISABEL</t>
+          <t>C001301555 - AGURTO SANTOS JESSICA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4808,11 +4804,11 @@
         <v>46235</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>46242</v>
+        <v>46238</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>S17732719</t>
+          <t>S17589351</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4822,11 +4818,11 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -4835,7 +4831,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4865,16 +4861,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>36090</v>
+        <v>18638</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4899,17 +4895,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C001628093</t>
+          <t>C001173438</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C001628093 - CRUZ MORANTE LUIS</t>
+          <t>C001173438 - RIOS HERRERA MARIA ELOISA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4924,11 +4920,11 @@
         <v>46235</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>S17730841</t>
+          <t>S17843740</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4938,11 +4934,11 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4951,7 +4947,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4981,7 +4977,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>28142</v>
+        <v>12814</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5015,12 +5011,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>C001521360</t>
+          <t>C001328215</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C001521360 - CARLOS DE LA CRUZ SERGIO</t>
+          <t>C001328215 - SANDOVAL DE SANTISTEBAN ANA MARIA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5040,11 +5036,11 @@
         <v>46235</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>S17617098</t>
+          <t>S17802768</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5090,23 +5086,23 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20014</v>
+        <v>10038</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5131,12 +5127,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C001301555</t>
+          <t>C001224721</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C001301555 - AGURTO SANTOS JESSICA</t>
+          <t>C001224721 - ROJAS PRAVIA MARIA MERCEDES</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5156,11 +5152,11 @@
         <v>46235</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>S17589351</t>
+          <t>S17616806</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5170,11 +5166,11 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -5183,7 +5179,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5213,16 +5209,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>18638</v>
+        <v>17415</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5247,12 +5243,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C001173438</t>
+          <t>C001405878</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C001173438 - RIOS HERRERA MARIA ELOISA</t>
+          <t>C001405878 - FLORES OLIVA HUGO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5272,11 +5268,11 @@
         <v>46235</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>46247</v>
+        <v>46239</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>S17843740</t>
+          <t>S17617793</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5286,11 +5282,11 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -5299,7 +5295,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5329,7 +5325,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>12814</v>
+        <v>110156</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5363,12 +5359,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C001328215</t>
+          <t>C001553531</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>C001328215 - SANDOVAL DE SANTISTEBAN ANA MARIA</t>
+          <t>C001553531 - RIVAS ARRIAGA JOSE RICARDO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5388,11 +5384,11 @@
         <v>46235</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>S17802768</t>
+          <t>S17623184</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5438,14 +5434,14 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10038</v>
+        <v>111438</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5479,12 +5475,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C001224721</t>
+          <t>C001274655</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C001224721 - ROJAS PRAVIA MARIA MERCEDES</t>
+          <t>C001274655 - MARTINEZ SOPLAPUCO PEDRO</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5504,11 +5500,11 @@
         <v>46235</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>S17616806</t>
+          <t>S17593174</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5531,7 +5527,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5539,7 +5535,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
@@ -5561,7 +5561,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17415</v>
+        <v>82417</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5595,12 +5595,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C001405878</t>
+          <t>C004180367</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C001405878 - FLORES OLIVA HUGO</t>
+          <t>C004180367 - HUAYTAN CAICEDO WALTER ORLANDO</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5620,11 +5620,11 @@
         <v>46235</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>S17617793</t>
+          <t>S17673606</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5677,7 +5677,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14022</v>
+        <v>71597</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5711,12 +5711,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>C001216357</t>
+          <t>C004160837</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>C001216357 - CRUZ MEZA NELLY AIDEE</t>
+          <t>C004160837 - UTIA TUANAMA KELI</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5736,11 +5736,11 @@
         <v>46235</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>S17585447</t>
+          <t>S17555609</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5771,7 +5771,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
@@ -5793,7 +5797,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>12701</v>
+        <v>67975</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5817,22 +5821,22 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>C001079831</t>
+          <t>C004168173</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>C001079831 - LLONTO CAJUSOL MARIA LINDAURA</t>
+          <t>C004168173 - SAAVEDRA RAMIREZ SOLEDAD</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5852,11 +5856,11 @@
         <v>46235</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>46246</v>
+        <v>46237</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>S17828420</t>
+          <t>S17571119</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5879,7 +5883,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5890,23 +5894,35 @@
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>32926</v>
+        <v>69829</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5931,17 +5947,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>C001079729</t>
+          <t>C004096900</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C001079729 - DUEÑAS DIAZ ROBERTO</t>
+          <t>C004096900 - CIEZA OYOLA BRAYAN ALONSO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5956,11 +5972,11 @@
         <v>46235</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>S17803851</t>
+          <t>S17597889</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5970,11 +5986,11 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -5983,7 +5999,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6013,7 +6029,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>32058</v>
+        <v>87502</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -6037,27 +6053,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C001523972</t>
+          <t>C004243081</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>C001523972 - OFERTAS Y NOVEDADES EL AS S.R.L.</t>
+          <t>C004243081 - ZENA ACOSTA JOSE LUIS</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6072,11 +6088,11 @@
         <v>46235</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>S17806202</t>
+          <t>S17723419</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6086,11 +6102,11 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -6099,7 +6115,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6110,23 +6126,35 @@
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>44182</v>
+        <v>95460</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6151,17 +6179,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C001661905</t>
+          <t>C001655917</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C001661905 - GRADOS VENTOSILLA MARISOL</t>
+          <t>C001655917 - CHINCHAY VALENCIA MARIA CLEOFILDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6176,11 +6204,11 @@
         <v>46235</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>S17559913</t>
+          <t>S17710431</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6190,11 +6218,11 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -6203,7 +6231,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6213,19 +6241,19 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6237,16 +6265,16 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>63976</v>
+        <v>106910</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6261,22 +6289,22 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>C004160232</t>
+          <t>C001286844</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>C004160232 - MOLOCHO LOZADA ERLA</t>
+          <t>C001286844 - MORA DE LA CRUZ ADELAIDA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6296,11 +6324,11 @@
         <v>46235</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>S17563886</t>
+          <t>S17620093</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6310,11 +6338,11 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -6331,29 +6359,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>71597</v>
+        <v>108773</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6387,12 +6407,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>C004160837</t>
+          <t>C001088415</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>C004160837 - UTIA TUANAMA KELI</t>
+          <t>C001088415 - JUAREZ VELASCO ROSA MARIA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6412,11 +6432,11 @@
         <v>46235</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>S17555609</t>
+          <t>S17591565</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6439,7 +6459,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6447,16 +6467,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6473,16 +6489,16 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>67975</v>
+        <v>14022</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6507,12 +6523,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C004168173</t>
+          <t>C001216357</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C004168173 - SAAVEDRA RAMIREZ SOLEDAD</t>
+          <t>C001216357 - CRUZ MEZA NELLY AIDEE</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6532,11 +6548,11 @@
         <v>46235</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>S17571119</t>
+          <t>S17585447</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6546,11 +6562,11 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -6589,16 +6605,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>69829</v>
+        <v>12701</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6613,22 +6629,22 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C004096900</t>
+          <t>C001079831</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>C004096900 - CIEZA OYOLA BRAYAN ALONSO</t>
+          <t>C001079831 - LLONTO CAJUSOL MARIA LINDAURA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6648,11 +6664,11 @@
         <v>46235</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>S17597889</t>
+          <t>S17828420</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6662,11 +6678,11 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R53" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -6675,7 +6691,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6686,26 +6702,14 @@
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>87502</v>
+        <v>32926</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6739,12 +6743,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>C004243081</t>
+          <t>C001079729</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C004243081 - ZENA ACOSTA JOSE LUIS</t>
+          <t>C001079729 - DUEÑAS DIAZ ROBERTO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6764,11 +6768,11 @@
         <v>46235</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>S17723419</t>
+          <t>S17803851</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6821,7 +6825,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>95460</v>
+        <v>32058</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6845,22 +6849,22 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>C001655917</t>
+          <t>C001523972</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C001655917 - CHINCHAY VALENCIA MARIA CLEOFILDA</t>
+          <t>C001523972 - OFERTAS Y NOVEDADES EL AS S.R.L.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6880,11 +6884,11 @@
         <v>46235</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>S17710431</t>
+          <t>S17806202</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6907,7 +6911,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6915,42 +6919,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>106910</v>
+        <v>44182</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6965,27 +6953,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C001286844</t>
+          <t>C001661905</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C001286844 - MORA DE LA CRUZ ADELAIDA</t>
+          <t>C001661905 - GRADOS VENTOSILLA MARISOL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7000,11 +6988,11 @@
         <v>46235</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>S17620093</t>
+          <t>S17559913</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7014,11 +7002,11 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -7042,14 +7030,26 @@
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Ver promociones</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>108773</v>
+        <v>63976</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7083,12 +7083,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>C001088415</t>
+          <t>C004160232</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C001088415 - JUAREZ VELASCO ROSA MARIA</t>
+          <t>C004160232 - MOLOCHO LOZADA ERLA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7108,11 +7108,11 @@
         <v>46235</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>S17591565</t>
+          <t>S17563886</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7165,16 +7165,16 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>98449</v>
+        <v>64653</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7189,22 +7189,22 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>C001414604</t>
+          <t>C004048977</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
+          <t>C004048977 - PURIHUAMAN MANAYAY CECILIA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7224,11 +7224,11 @@
         <v>46235</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>S17532338</t>
+          <t>S17656496</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7238,11 +7238,11 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -7266,26 +7266,14 @@
       </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>86037</v>
+        <v>59715</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7309,27 +7297,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>C004218405</t>
+          <t>C004164415</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C004218405 - SUCLUPE LOPEZ WILLIAN ALBERTO</t>
+          <t>C004164415 - MANAYAY DE LOS SANTOS GERMAN OSCAR</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7344,11 +7332,11 @@
         <v>46235</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>S17752069</t>
+          <t>S17563560</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7358,11 +7346,11 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -7371,7 +7359,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7379,33 +7367,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>90366</v>
+        <v>45047</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7439,12 +7411,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>C001691302</t>
+          <t>C001723751</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C001691302 - BERNILLA GARCIA ESTHER JHONA</t>
+          <t>C001723751 - PAREDES DE ESPINOZA MARIA DEL ELMA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7468,7 +7440,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>S17569141</t>
+          <t>S17567021</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7491,7 +7463,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7521,7 +7493,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>78372</v>
+        <v>50204</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7555,17 +7527,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C004237053</t>
+          <t>C001718760</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>C004237053 - MENDO LLAGUENTO FANNY ISABEL</t>
+          <t>C001718760 - GUEVARA MONJE CELINDA IRENE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7580,11 +7552,11 @@
         <v>46235</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>S17666012</t>
+          <t>S17566592</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7594,11 +7566,11 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -7615,7 +7587,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr">
@@ -7637,7 +7613,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>64653</v>
+        <v>35017</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7661,22 +7637,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>C004048977</t>
+          <t>C001570988</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>C004048977 - PURIHUAMAN MANAYAY CECILIA</t>
+          <t>C001570988 - CASTRO PISCOYA WILLIAN YOVANI</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7696,11 +7672,11 @@
         <v>46235</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>S17656496</t>
+          <t>S17572856</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7723,7 +7699,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7731,21 +7707,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>59715</v>
+        <v>28193</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7774,17 +7758,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>C004164415</t>
+          <t>C001284564</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>C004164415 - MANAYAY DE LOS SANTOS GERMAN OSCAR</t>
+          <t>C001284564 - MANAYAY SOTO MARI CRUZ YESIBEL</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7808,7 +7792,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>S17563560</t>
+          <t>S17569978</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7849,16 +7833,16 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>45047</v>
+        <v>28729</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7883,12 +7867,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>C001723751</t>
+          <t>C001545229</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>C001723751 - PAREDES DE ESPINOZA MARIA DEL ELMA</t>
+          <t>C001545229 - VALLEJOS DIAZ MARIA CANDELARIA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7908,11 +7892,11 @@
         <v>46235</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>S17567021</t>
+          <t>S17543503</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7922,11 +7906,11 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -7935,7 +7919,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7948,7 +7932,7 @@
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -7965,7 +7949,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>50204</v>
+        <v>28139</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7989,27 +7973,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>C001718760</t>
+          <t>C001516332</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C001718760 - GUEVARA MONJE CELINDA IRENE</t>
+          <t>C001516332 - CARMONA ROJAS MAGALI LUCILA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1000009104</t>
+          <t>1000049464</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8028,7 +8012,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>S17566592</t>
+          <t>S17552441</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8038,11 +8022,11 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -8061,31 +8045,19 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>35017</v>
+        <v>23284</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8119,12 +8091,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>C001570988</t>
+          <t>C001487761</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>C001570988 - CASTRO PISCOYA WILLIAN YOVANI</t>
+          <t>C001487761 - TORRES HEREDIA ENNA ROXANA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8148,7 +8120,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>S17572856</t>
+          <t>S17569131</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8171,7 +8143,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -8189,7 +8161,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8201,16 +8173,16 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>28193</v>
+        <v>98449</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AXEL ALAIN RENTERIA GUEVARA</t>
+          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>77670826</t>
+          <t>40149954</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8225,22 +8197,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>C001284564</t>
+          <t>C001414604</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>C001284564 - MANAYAY SOTO MARI CRUZ YESIBEL</t>
+          <t>C001414604 - VASQUEZ RAMIREZ YENY CARINA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8260,11 +8232,11 @@
         <v>46235</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>S17569978</t>
+          <t>S17532338</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8274,11 +8246,11 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R67" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -8295,17 +8267,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>28139</v>
+        <v>86037</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -8329,27 +8317,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>C001516332</t>
+          <t>C004218405</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>C001516332 - CARMONA ROJAS MAGALI LUCILA</t>
+          <t>C004218405 - SUCLUPE LOPEZ WILLIAN ALBERTO</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1000049464</t>
+          <t>1000009104</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8364,11 +8352,11 @@
         <v>46235</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>S17552441</t>
+          <t>S17752069</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8378,11 +8366,11 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000009104</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -8391,7 +8379,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8401,28 +8389,40 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>28729</v>
+        <v>90366</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HILDA YOLANDA VIGIL VASQUEZ</t>
+          <t>AXEL ALAIN RENTERIA GUEVARA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>40149954</t>
+          <t>77670826</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>C001545229</t>
+          <t>C001691302</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>C001545229 - VALLEJOS DIAZ MARIA CANDELARIA</t>
+          <t>C001691302 - BERNILLA GARCIA ESTHER JHONA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8472,11 +8472,11 @@
         <v>46235</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>S17543503</t>
+          <t>S17569141</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8486,11 +8486,11 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>40149954CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
+          <t>77670826CHICLAYOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000049464</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -8529,7 +8529,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>23284</v>
+        <v>78372</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -8563,12 +8563,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>C001487761</t>
+          <t>C004237053</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>C001487761 - TORRES HEREDIA ENNA ROXANA</t>
+          <t>C004237053 - MENDO LLAGUENTO FANNY ISABEL</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8588,11 +8588,11 @@
         <v>46235</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>S17569131</t>
+          <t>S17666012</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
